--- a/results/job_matches_2026-06-10.xlsx
+++ b/results/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Software Engineer III - Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
+          <t>https://www.indeed.com/viewjob?jk=85cdeb8503f6c459</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
+          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
+          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
+          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Software Engineer, Senior</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212d73dd2934b416</t>
+          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Databricks)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Databricks)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
+          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,112 +1081,112 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
+          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
+          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>API Integrations Developer</t>
+          <t>Developer-Full Stack Professional</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Colorado Access</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd682ad6ededbf7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Developer-Full Stack Senior</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2f3d539abd0b18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Data Architect / Enterprise Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chaska, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3d42860bcdf47</t>
+          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HealthStream</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Medisolv Inc</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
+          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Site Reliability</t>
+          <t>GCP Data Architect / Enterprise Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Syniti</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chaska, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3d42860bcdf47</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETL Engineer_Woonsocket, RI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
+          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
+          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Database Developer, PostgreSQL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Midwest Tape</t>
+          <t>Medisolv Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holland, OH, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1529c26a5cedd185</t>
+          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Sr. Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Syniti</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Senior Analytics Engineer (Breakthrough)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Powertrain Embedded ASW , DevOps and Compiler Toolchain Engineer</t>
+          <t>ETL Engineer_Woonsocket, RI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022045c10afd20b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Digital Consultants</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Breakthrough)</t>
+          <t>GTM DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>ClickUp</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
+          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Senior Database Developer, PostgreSQL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Midwest Tape</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Holland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, Step Functions, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+          <t>https://www.indeed.com/viewjob?jk=1529c26a5cedd185</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
+          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mongo Data Engineer</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
+          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Powertrain Embedded ASW , DevOps and Compiler Toolchain Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PineCone</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
+          <t>https://www.indeed.com/viewjob?jk=022045c10afd20b1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
+          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Production Digitalization Intern (Fall 2026)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Woodruff, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
+          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Mongo Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f560ecbc79fa34</t>
+          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>PineCone</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETL with Sql Developer</t>
+          <t>Associate Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06bbe197dd700f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Production Digitalization Intern (Fall 2026)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>BMW Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Woodruff, SC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Application Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>PaceMate™</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
+          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>ETL with Sql Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cypress, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
+          <t>https://www.indeed.com/viewjob?jk=d06bbe197dd700f6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abed50f2367d51</t>
+          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect, Customer Success - US (Remote)</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer, Supply Chain</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, ETL, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216432e17bbf1a19</t>
+          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer - Core Platform Integration</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Cypress, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
+          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Solutions Architect, Customer Success - US (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda9e03abcd1738f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Power BI Engineer</t>
+          <t>Data Engineer, Supply Chain</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hussmann</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bridgeton, MO, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Scala, PostgreSQL, ETL, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
+          <t>https://www.indeed.com/viewjob?jk=216432e17bbf1a19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Sr Software Development Engineer - Core Platform Integration</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74b9cddc3c99f92</t>
+          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GCP data architect with Google MDE</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chaska, MN, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Airflow, Python</t>
+          <t>AWS, S3, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7204abc945e17f46</t>
+          <t>https://www.indeed.com/viewjob?jk=fda9e03abcd1738f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Sr. Power BI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Hussmann</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgeton, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
+          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Application Developer - ICTS Biomedical Informatics</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The University of Iowa</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iowa City, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Power BI, Tableau, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4e0068d45e0271</t>
+          <t>https://www.indeed.com/viewjob?jk=b74b9cddc3c99f92</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>GCP data architect with Google MDE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chaska, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Airflow, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=7204abc945e17f46</t>
         </is>
       </c>
     </row>
@@ -2638,25 +2638,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Serverless Full Stack Engineer</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Amazon QuickSight</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II, Wayfair Sponsored Shops</t>
+          <t>AWS Serverless Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
+          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
+          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Customer Data Platform Data Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ARUP Laboratories</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Expert Site Reliability Engineer</t>
+          <t>Customer Data Platform Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Altera Digital Health</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6727c6b22ae8047e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>ARUP Laboratories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Priwils</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f30acbe9dfb62b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4009f7a34c3ab8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Automation Test Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
+          <t>https://www.indeed.com/viewjob?jk=62889aa5922edf0b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cc2c66ba0e93b9</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62889aa5922edf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0092e012c75cc2a</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cc2c66ba0e93b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a414e5a1b8554cba</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0092e012c75cc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3624cd7b0a14b1d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a414e5a1b8554cba</t>
+          <t>https://www.indeed.com/viewjob?jk=537b772ef1ebe9ee</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b772ef1ebe9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=493c0396fe981250</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493c0396fe981250</t>
+          <t>https://www.indeed.com/viewjob?jk=d96b2c55a546723e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96b2c55a546723e</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea64f7ee5edd31</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8516e11f84de36e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0edf7a2d9633e5a</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3a7be56c01f917</t>
+          <t>https://www.indeed.com/viewjob?jk=a8516e11f84de36e</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623bb336cc90d3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3a7be56c01f917</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f04f24aa16c1bb</t>
+          <t>https://www.indeed.com/viewjob?jk=623bb336cc90d3f0</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b156cbe16df965f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f04f24aa16c1bb</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b427b79fadeaeca</t>
+          <t>https://www.indeed.com/viewjob?jk=b156cbe16df965f9</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3706793e6a0524a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b427b79fadeaeca</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479e0d19944e1a77</t>
+          <t>https://www.indeed.com/viewjob?jk=b3706793e6a0524a</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bed7e6546b8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=6a90f94e3442f55d</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff5839e147b0f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=479e0d19944e1a77</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb723b7e8b1af2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=21bed7e6546b8e41</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1824380acb61d226</t>
+          <t>https://www.indeed.com/viewjob?jk=39c2bb9cf80e320f</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cade42e913d0662e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff5839e147b0f9e</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019e10b76f1f876c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb723b7e8b1af2fb</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31bd25bae6c274f5</t>
+          <t>https://www.indeed.com/viewjob?jk=1824380acb61d226</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a403a9c1d876e0</t>
+          <t>https://www.indeed.com/viewjob?jk=cade42e913d0662e</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bbe0f642103d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=019e10b76f1f876c</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d1424b74f3dedb</t>
+          <t>https://www.indeed.com/viewjob?jk=31bd25bae6c274f5</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05574fa4cad0fc37</t>
+          <t>https://www.indeed.com/viewjob?jk=ddef646960a8a8d3</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac37ab0081e2642d</t>
+          <t>https://www.indeed.com/viewjob?jk=99a403a9c1d876e0</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a593dea989cf8f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=83bbe0f642103d2c</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba8829787244a47</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d1424b74f3dedb</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4009f7a34c3ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=05574fa4cad0fc37</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3624cd7b0a14b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac37ab0081e2642d</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea64f7ee5edd31</t>
+          <t>https://www.indeed.com/viewjob?jk=a593dea989cf8f2b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0edf7a2d9633e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba8829787244a47</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Automation Test Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a90f94e3442f55d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c2bb9cf80e320f</t>
+          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,42 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddef646960a8a8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f30acbe9dfb62b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Expert Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Altera Digital Health</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6727c6b22ae8047e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-10.xlsx
+++ b/results/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
+          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Senior Data Engineer, Growth, Insights &amp; Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Edgewell Personal Care</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
+          <t>https://www.indeed.com/viewjob?jk=4935b0927c3cb923</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
+          <t>https://www.indeed.com/viewjob?jk=4692482ce562c2f3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>SENIOR DATA ENGINEER-REMOTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cdai</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
+          <t>https://www.indeed.com/viewjob?jk=8d77a89c68dff947</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
+          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4692482ce562c2f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER-REMOTE</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cdai</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d77a89c68dff947</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Databricks)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
+          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c118f0ba65ed66</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
+          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Databricks)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,137 +1056,137 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ernest Talent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Developer-Full Stack Professional</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd682ad6ededbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Developer-Full Stack Senior</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2f3d539abd0b18</t>
+          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Data Architect / Enterprise Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Chaska, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,89 +1266,89 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3d42860bcdf47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
+          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
+          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
+          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Medisolv Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,172 +1406,172 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
+          <t>https://www.indeed.com/viewjob?jk=519f9316645f657a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP Data Architect / Enterprise Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chaska, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3d42860bcdf47</t>
+          <t>https://www.indeed.com/viewjob?jk=d7737db6448a1bfd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
+          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Breakthrough)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Medisolv Inc</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
+          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Site Reliability</t>
+          <t>ETL Engineer_Woonsocket, RI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Syniti</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Breakthrough)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
+          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETL Engineer_Woonsocket, RI</t>
+          <t>GTM DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>ClickUp</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
+          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Database Developer, PostgreSQL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Midwest Tape</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Holland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, Step Functions, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
+          <t>https://www.indeed.com/viewjob?jk=1529c26a5cedd185</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GTM DevOps Engineer</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
+          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Database Developer, PostgreSQL</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Midwest Tape</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Holland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1529c26a5cedd185</t>
+          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
+          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Mongo Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
+          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Powertrain Embedded ASW , DevOps and Compiler Toolchain Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>PineCone</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022045c10afd20b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Associate Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
+          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mongo Data Engineer</t>
+          <t>Ping Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Associate Application Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PineCone</t>
+          <t>PaceMate™</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
+          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
+          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Production Digitalization Intern (Fall 2026)</t>
+          <t>Solutions Architect, Customer Success - US (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Woodruff, SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
+          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Application Engineer – AI &amp; Data</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PaceMate™</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETL with Sql Developer</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06bbe197dd700f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Sr Software Development Engineer - Core Platform Integration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
+          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
+          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b74b9cddc3c99f92</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP data architect with Google MDE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chaska, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Airflow, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
+          <t>https://www.indeed.com/viewjob?jk=7204abc945e17f46</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cypress, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
+          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect, Customer Success - US (Remote)</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer, Supply Chain</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, ETL, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216432e17bbf1a19</t>
+          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer - Core Platform Integration</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Serverless Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,54 +2491,54 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda9e03abcd1738f</t>
+          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Power BI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hussmann</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bridgeton, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
+          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2547,46 +2547,46 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74b9cddc3c99f92</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP data architect with Google MDE</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chaska, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Airflow, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7204abc945e17f46</t>
+          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Customer Data Platform Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
+          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
+          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Serverless Full Stack Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>ARUP Laboratories</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Amazon QuickSight</t>
+          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Priwils</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4009f7a34c3ab8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
+          <t>https://www.indeed.com/viewjob?jk=62889aa5922edf0b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cc2c66ba0e93b9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Customer Data Platform Data Engineer (Hybrid)</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0092e012c75cc2a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ARUP Laboratories</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
+          <t>https://www.indeed.com/viewjob?jk=a414e5a1b8554cba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Priwils</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c3624cd7b0a14b1d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4009f7a34c3ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=537b772ef1ebe9ee</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62889aa5922edf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=493c0396fe981250</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cc2c66ba0e93b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d96b2c55a546723e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0092e012c75cc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea64f7ee5edd31</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a414e5a1b8554cba</t>
+          <t>https://www.indeed.com/viewjob?jk=64740ad782df5cb1</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3624cd7b0a14b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6eeb799e5eab4148</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b772ef1ebe9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2bd983231800dd</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493c0396fe981250</t>
+          <t>https://www.indeed.com/viewjob?jk=8153722997cb57af</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96b2c55a546723e</t>
+          <t>https://www.indeed.com/viewjob?jk=082451c1b3ac524d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea64f7ee5edd31</t>
+          <t>https://www.indeed.com/viewjob?jk=2b32a5cd05c4b385</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64740ad782df5cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=509553f5b2b80b93</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eeb799e5eab4148</t>
+          <t>https://www.indeed.com/viewjob?jk=4024b03d5ccdbe7b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2bd983231800dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b77131ae6dad4a04</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8153722997cb57af</t>
+          <t>https://www.indeed.com/viewjob?jk=10a8d31d11a2ba88</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082451c1b3ac524d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6b64cd60eee8fc</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b32a5cd05c4b385</t>
+          <t>https://www.indeed.com/viewjob?jk=86d0f0a4bb5ca18b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=509553f5b2b80b93</t>
+          <t>https://www.indeed.com/viewjob?jk=32e597607c22e457</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4024b03d5ccdbe7b</t>
+          <t>https://www.indeed.com/viewjob?jk=165543ad99d2740a</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77131ae6dad4a04</t>
+          <t>https://www.indeed.com/viewjob?jk=b070a38d68a94065</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a8d31d11a2ba88</t>
+          <t>https://www.indeed.com/viewjob?jk=a567d090bf66c662</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6b64cd60eee8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c09b7c00e3d2c83e</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d0f0a4bb5ca18b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0f53deb4a9b18b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e597607c22e457</t>
+          <t>https://www.indeed.com/viewjob?jk=f0edf7a2d9633e5a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=165543ad99d2740a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8516e11f84de36e</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b070a38d68a94065</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3a7be56c01f917</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a567d090bf66c662</t>
+          <t>https://www.indeed.com/viewjob?jk=623bb336cc90d3f0</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09b7c00e3d2c83e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f04f24aa16c1bb</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0f53deb4a9b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=b156cbe16df965f9</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0edf7a2d9633e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b427b79fadeaeca</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8516e11f84de36e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3706793e6a0524a</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3a7be56c01f917</t>
+          <t>https://www.indeed.com/viewjob?jk=6a90f94e3442f55d</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623bb336cc90d3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=479e0d19944e1a77</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f04f24aa16c1bb</t>
+          <t>https://www.indeed.com/viewjob?jk=21bed7e6546b8e41</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b156cbe16df965f9</t>
+          <t>https://www.indeed.com/viewjob?jk=39c2bb9cf80e320f</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b427b79fadeaeca</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff5839e147b0f9e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3706793e6a0524a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb723b7e8b1af2fb</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a90f94e3442f55d</t>
+          <t>https://www.indeed.com/viewjob?jk=1824380acb61d226</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479e0d19944e1a77</t>
+          <t>https://www.indeed.com/viewjob?jk=cade42e913d0662e</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bed7e6546b8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=019e10b76f1f876c</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c2bb9cf80e320f</t>
+          <t>https://www.indeed.com/viewjob?jk=31bd25bae6c274f5</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff5839e147b0f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ddef646960a8a8d3</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb723b7e8b1af2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=99a403a9c1d876e0</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1824380acb61d226</t>
+          <t>https://www.indeed.com/viewjob?jk=83bbe0f642103d2c</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cade42e913d0662e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d1424b74f3dedb</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019e10b76f1f876c</t>
+          <t>https://www.indeed.com/viewjob?jk=05574fa4cad0fc37</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31bd25bae6c274f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac37ab0081e2642d</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddef646960a8a8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a593dea989cf8f2b</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a403a9c1d876e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba8829787244a47</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bbe0f642103d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Automation Test Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d1424b74f3dedb</t>
+          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05574fa4cad0fc37</t>
+          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,217 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac37ab0081e2642d</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a593dea989cf8f2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba8829787244a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Automation Test Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Qualitest</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3f30acbe9dfb62b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Expert Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Altera Digital Health</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6727c6b22ae8047e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-10.xlsx
+++ b/results/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
+          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
+          <t>https://www.indeed.com/viewjob?jk=4692482ce562c2f3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Growth, Insights &amp; Analytics</t>
+          <t>SENIOR DATA ENGINEER-REMOTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edgewell Personal Care</t>
+          <t>Cdai</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4935b0927c3cb923</t>
+          <t>https://www.indeed.com/viewjob?jk=8d77a89c68dff947</t>
         </is>
       </c>
     </row>
@@ -683,20 +683,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4692482ce562c2f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER-REMOTE</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cdai</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d77a89c68dff947</t>
+          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, ECS, IAM, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
+          <t>https://www.indeed.com/viewjob?jk=67874b8838f9d9a8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (AWS, Databricks)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
+          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Databricks)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c118f0ba65ed66</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
+          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Ernest Talent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c118f0ba65ed66</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ernest Talent</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qeexo, Co.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Clemente, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
+          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
+          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
+          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Data Architect / Enterprise Architect</t>
+          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chaska, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3d42860bcdf47</t>
+          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer | Bankrate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
+          <t>https://www.indeed.com/viewjob?jk=8423ebd744ce429c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Medisolv Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
+          <t>https://www.indeed.com/viewjob?jk=519f9316645f657a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Medisolv Inc</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
+          <t>https://www.indeed.com/viewjob?jk=d7737db6448a1bfd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,52 +1431,52 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, dbt, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519f9316645f657a</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e19b901655965</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7737db6448a1bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
+          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analytics Engineer (Breakthrough)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Breakthrough)</t>
+          <t>ETL Engineer_Woonsocket, RI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
+          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETL Engineer_Woonsocket, RI</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
+          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>GTM DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>ClickUp</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
+          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GTM DevOps Engineer</t>
+          <t>Senior Database Developer, PostgreSQL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>Midwest Tape</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Holland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, Step Functions, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
+          <t>https://www.indeed.com/viewjob?jk=1529c26a5cedd185</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Database Developer, PostgreSQL</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Midwest Tape</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Holland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1529c26a5cedd185</t>
+          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
         </is>
       </c>
     </row>
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
+          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
+          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mongo Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
+          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mongo Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PineCone</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PineCone</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
+          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Ping Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Associate Application Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>PaceMate™</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ping Engineer</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
+          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Application Engineer – AI &amp; Data</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PaceMate™</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>ETL with Sql Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d06bbe197dd700f6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Architect, Customer Success - US (Remote)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
+          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>Solutions Architect, Customer Success - US (Remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP data architect with Google MDE</t>
+          <t>Full Stack- FDE EST</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chaska, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Airflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7204abc945e17f46</t>
+          <t>https://www.indeed.com/viewjob?jk=8a24df4c2a49d56a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
         </is>
       </c>
     </row>
@@ -4878,33 +4878,68 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Charlotte, NC, US USA</t>
         </is>
       </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3f30acbe9dfb62b5</t>
         </is>

--- a/results/job_matches_2026-06-10.xlsx
+++ b/results/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Exaways Corporation</t>
+          <t>Pavago</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf85c1090a97cd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=424cfabc18b01038</t>
         </is>
       </c>
     </row>
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>GCP DATA ENGINEER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
+          <t>https://www.indeed.com/viewjob?jk=e23ead1703b573ed</t>
         </is>
       </c>
     </row>
@@ -713,35 +713,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Luminie Studio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=11fa7f32e5b49cfa</t>
         </is>
       </c>
     </row>
@@ -923,95 +923,95 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
+          <t>https://www.indeed.com/viewjob?jk=caf37a9b3156f8dd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ernest Talent</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcb0ad10b28a6f6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
+          <t>https://www.indeed.com/viewjob?jk=38db06205a3e4bf5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b6929e731217b8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f1182f80665686</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qeexo, Co.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Clemente, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1adbdb2bdac0514f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
+          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Luminie Studio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,81 +1182,81 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Ernest Talent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Bankrate</t>
+          <t>Senior Engineer .Net Full-Stack</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,207 +1301,207 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8423ebd744ce429c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8584f1ea91ecab5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Medisolv Inc</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
+          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519f9316645f657a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7737db6448a1bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, dbt, Power BI, Tableau, MLflow</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e19b901655965</t>
+          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Qeexo, Co.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Clemente, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Breakthrough)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
+          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETL Engineer_Woonsocket, RI</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
+          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
+          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GTM DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
+          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Database Developer, PostgreSQL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Midwest Tape</t>
+          <t>Medisolv Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Holland, OH, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,242 +1686,242 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1529c26a5cedd185</t>
+          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
+          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Cloud Solutions Architect 3 (Contractor) 529701735</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>IAM, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1b55eb58f3e1bbe2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
+          <t>https://www.indeed.com/viewjob?jk=519f9316645f657a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mongo Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
+          <t>https://www.indeed.com/viewjob?jk=d7737db6448a1bfd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PineCone</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
+          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ping Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, S3, HDFS, Hive, Spark, Scala, PostgreSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Application Engineer – AI &amp; Data</t>
+          <t>Senior Analytics Engineer (Breakthrough)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PaceMate™</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>ETL Engineer_Woonsocket, RI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
+          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,49 +2001,49 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
+          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETL with Sql Developer</t>
+          <t>Java Full Stack Senior Developer/Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,85 +2053,85 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06bbe197dd700f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e3684f4d626ff94f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Java Full Stack Senior Developer/Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e87ee2317bc76f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solutions Architect, Customer Success - US (Remote)</t>
+          <t>GTM DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>ClickUp</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
+          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Holistic Partners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer - Core Platform Integration</t>
+          <t>Data Engineer – Data Integration (Remote)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
+          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
+          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Mongo Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74b9cddc3c99f92</t>
+          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack- FDE EST</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>PineCone</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a24df4c2a49d56a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Ping Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Associate Application Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>PaceMate™</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
+          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Serverless Full Stack Engineer</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Amazon QuickSight</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,207 +2491,207 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
+          <t>Solutions Architect, Customer Success - US (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Manger, Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Development Engineer - Core Platform Integration</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,102 +2701,102 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
+          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Customer Data Platform Data Engineer (Hybrid)</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ARUP Laboratories</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
+          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,54 +2806,54 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
+          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Priwils</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Application Developer – Microsoft .NET (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4009f7a34c3ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62889aa5922edf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,94 +2981,94 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cc2c66ba0e93b9</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Full Stack- FDE EST</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0092e012c75cc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a24df4c2a49d56a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a414e5a1b8554cba</t>
+          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3624cd7b0a14b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b772ef1ebe9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493c0396fe981250</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96b2c55a546723e</t>
+          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea64f7ee5edd31</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64740ad782df5cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eeb799e5eab4148</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Customer Data Platform Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2bd983231800dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ARUP Laboratories</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8153722997cb57af</t>
+          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082451c1b3ac524d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b32a5cd05c4b385</t>
+          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Priwils</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=509553f5b2b80b93</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4024b03d5ccdbe7b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4009f7a34c3ab8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77131ae6dad4a04</t>
+          <t>https://www.indeed.com/viewjob?jk=62889aa5922edf0b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a8d31d11a2ba88</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cc2c66ba0e93b9</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6b64cd60eee8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0092e012c75cc2a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d0f0a4bb5ca18b</t>
+          <t>https://www.indeed.com/viewjob?jk=a414e5a1b8554cba</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e597607c22e457</t>
+          <t>https://www.indeed.com/viewjob?jk=c3624cd7b0a14b1d</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=165543ad99d2740a</t>
+          <t>https://www.indeed.com/viewjob?jk=537b772ef1ebe9ee</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b070a38d68a94065</t>
+          <t>https://www.indeed.com/viewjob?jk=493c0396fe981250</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a567d090bf66c662</t>
+          <t>https://www.indeed.com/viewjob?jk=d96b2c55a546723e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09b7c00e3d2c83e</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea64f7ee5edd31</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0f53deb4a9b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=64740ad782df5cb1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0edf7a2d9633e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=6eeb799e5eab4148</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8516e11f84de36e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2bd983231800dd</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3a7be56c01f917</t>
+          <t>https://www.indeed.com/viewjob?jk=8153722997cb57af</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623bb336cc90d3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=082451c1b3ac524d</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f04f24aa16c1bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2b32a5cd05c4b385</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b156cbe16df965f9</t>
+          <t>https://www.indeed.com/viewjob?jk=509553f5b2b80b93</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b427b79fadeaeca</t>
+          <t>https://www.indeed.com/viewjob?jk=4024b03d5ccdbe7b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3706793e6a0524a</t>
+          <t>https://www.indeed.com/viewjob?jk=b77131ae6dad4a04</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a90f94e3442f55d</t>
+          <t>https://www.indeed.com/viewjob?jk=10a8d31d11a2ba88</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479e0d19944e1a77</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6b64cd60eee8fc</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bed7e6546b8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=86d0f0a4bb5ca18b</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c2bb9cf80e320f</t>
+          <t>https://www.indeed.com/viewjob?jk=32e597607c22e457</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff5839e147b0f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=165543ad99d2740a</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb723b7e8b1af2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b070a38d68a94065</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1824380acb61d226</t>
+          <t>https://www.indeed.com/viewjob?jk=a567d090bf66c662</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cade42e913d0662e</t>
+          <t>https://www.indeed.com/viewjob?jk=c09b7c00e3d2c83e</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019e10b76f1f876c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0f53deb4a9b18b</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31bd25bae6c274f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f0edf7a2d9633e5a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddef646960a8a8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a8516e11f84de36e</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a403a9c1d876e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3a7be56c01f917</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bbe0f642103d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=623bb336cc90d3f0</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d1424b74f3dedb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f04f24aa16c1bb</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05574fa4cad0fc37</t>
+          <t>https://www.indeed.com/viewjob?jk=b156cbe16df965f9</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac37ab0081e2642d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b427b79fadeaeca</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a593dea989cf8f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3706793e6a0524a</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba8829787244a47</t>
+          <t>https://www.indeed.com/viewjob?jk=6a90f94e3442f55d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
+          <t>https://www.indeed.com/viewjob?jk=479e0d19944e1a77</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Automation Test Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
+          <t>https://www.indeed.com/viewjob?jk=21bed7e6546b8e41</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
+          <t>https://www.indeed.com/viewjob?jk=39c2bb9cf80e320f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff5839e147b0f9e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,532 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f30acbe9dfb62b5</t>
+          <t>https://www.indeed.com/viewjob?jk=eb723b7e8b1af2fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1824380acb61d226</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cade42e913d0662e</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=019e10b76f1f876c</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31bd25bae6c274f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddef646960a8a8d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99a403a9c1d876e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83bbe0f642103d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3d1424b74f3dedb</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05574fa4cad0fc37</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac37ab0081e2642d</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a593dea989cf8f2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ba8829787244a47</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Automation Test Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Qualitest</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-10.xlsx
+++ b/results/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luminie Studio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,52 +696,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
+          <t>https://www.indeed.com/viewjob?jk=11fa7f32e5b49cfa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luminie Studio</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, ECS, IAM, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fa7f32e5b49cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=67874b8838f9d9a8</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67874b8838f9d9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
+          <t>https://www.indeed.com/viewjob?jk=caf37a9b3156f8dd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Databricks)</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcb0ad10b28a6f6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c118f0ba65ed66</t>
+          <t>https://www.indeed.com/viewjob?jk=38db06205a3e4bf5</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -946,12 +946,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf37a9b3156f8dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b6929e731217b8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcb0ad10b28a6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f1182f80665686</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38db06205a3e4bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=1adbdb2bdac0514f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Developer-Full Stack Professional</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b6929e731217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd682ad6ededbf7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Developer-Full Stack Senior</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f1182f80665686</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2f3d539abd0b18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1adbdb2bdac0514f</t>
+          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer (AWS) - Remote Opportunity</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>Luminie Studio</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c211bb96fa54e53d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>RELTIO INTEGRATION HUB ENGINEER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luminie Studio</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
         </is>
       </c>
     </row>
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
+          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,69 +1571,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
+          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Medisolv Inc</t>
+          <t>Teambuilder</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d34ade42ca5e88</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
+          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 (Contractor) 529701735</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Medisolv Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT, Tableau</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b55eb58f3e1bbe2</t>
+          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519f9316645f657a</t>
+          <t>https://www.indeed.com/viewjob?jk=e500cf88e638ac7b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7737db6448a1bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef1bee76953de15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e996475c9120b1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=50c95bf56aa2f1bd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, HDFS, Hive, Spark, Scala, PostgreSQL, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Breakthrough)</t>
+          <t>Cloud Solutions Architect 3 (Contractor) 529701735</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
+          <t>IAM, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
+          <t>https://www.indeed.com/viewjob?jk=1b55eb58f3e1bbe2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ETL Engineer_Woonsocket, RI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
+          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
+          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Java Full Stack Senior Developer/Architect</t>
+          <t>Senior DevOps Engineer (On Site-Only)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>New York Cancer and Blood Specialists</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ridge, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3684f4d626ff94f</t>
+          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Full Stack Senior Developer/Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, S3, HDFS, Hive, Spark, Scala, PostgreSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e87ee2317bc76f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GTM DevOps Engineer</t>
+          <t>Senior Analytics Engineer (Breakthrough)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,172 +2141,172 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
+          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>ETL Engineer_Woonsocket, RI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Holistic Partners</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
+          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer – Data Integration (Remote)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Full Stack Senior Developer/Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
+          <t>https://www.indeed.com/viewjob?jk=e3684f4d626ff94f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mongo Data Engineer</t>
+          <t>Java Full Stack Senior Developer/Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e87ee2317bc76f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>GTM DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PineCone</t>
+          <t>ClickUp</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
+          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Holistic Partners</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ping Engineer</t>
+          <t>Data Engineer – Data Integration (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
+          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Application Engineer – AI &amp; Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PaceMate™</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Mongo Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
+          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>PineCone</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solutions Architect, Customer Success - US (Remote)</t>
+          <t>Ping Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,64 +2551,64 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Manger, Data Engineering</t>
+          <t>Associate Application Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>PaceMate™</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,81 +2617,81 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer - Core Platform Integration</t>
+          <t>Solutions Architect, Customer Success - US (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
+          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
+          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Senior Manger, Data Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Application Developer – Microsoft .NET (Remote)</t>
+          <t>Sr Software Development Engineer - Core Platform Integration</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
+          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
+          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack- FDE EST</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a24df4c2a49d56a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
+          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>cybertechnologyinnovations</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, SQL Server, MySQL, CloudWatch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,102 +3121,102 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e1a7ccf1662daf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Application Developer – Microsoft .NET (Remote)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,129 +3226,129 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack- FDE EST</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
+          <t>https://www.indeed.com/viewjob?jk=8a24df4c2a49d56a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
+          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Customer Data Platform Data Engineer (Hybrid)</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
+          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ARUP Laboratories</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
+          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Priwils</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
+          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4009f7a34c3ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62889aa5922edf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cc2c66ba0e93b9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0092e012c75cc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a414e5a1b8554cba</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Customer Data Platform Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3624cd7b0a14b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ARUP Laboratories</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b772ef1ebe9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Redshift, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, Talend</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493c0396fe981250</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc5438c12ec9d4a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96b2c55a546723e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea64f7ee5edd31</t>
+          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Priwils</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64740ad782df5cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eeb799e5eab4148</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Automation Test Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2bd983231800dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,1520 +3951,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8153722997cb57af</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=082451c1b3ac524d</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b32a5cd05c4b385</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=509553f5b2b80b93</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4024b03d5ccdbe7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b77131ae6dad4a04</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10a8d31d11a2ba88</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6b64cd60eee8fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Mechanicsburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86d0f0a4bb5ca18b</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32e597607c22e457</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=165543ad99d2740a</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b070a38d68a94065</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a567d090bf66c662</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c09b7c00e3d2c83e</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0f53deb4a9b18b</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0edf7a2d9633e5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8516e11f84de36e</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3a7be56c01f917</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=623bb336cc90d3f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Midland, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f04f24aa16c1bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b156cbe16df965f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b427b79fadeaeca</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3706793e6a0524a</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a90f94e3442f55d</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=479e0d19944e1a77</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21bed7e6546b8e41</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39c2bb9cf80e320f</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff5839e147b0f9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb723b7e8b1af2fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1824380acb61d226</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cade42e913d0662e</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=019e10b76f1f876c</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31bd25bae6c274f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddef646960a8a8d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99a403a9c1d876e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83bbe0f642103d2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d1424b74f3dedb</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05574fa4cad0fc37</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Fresno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac37ab0081e2642d</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a593dea989cf8f2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba8829787244a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Automation Test Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Qualitest</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Java Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
         </is>

--- a/results/job_matches_2026-06-10.xlsx
+++ b/results/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP DATA ENGINEER</t>
+          <t>Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23ead1703b573ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e12084d35df615</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP DATA ENGINEER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark, Kafka</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4692482ce562c2f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e23ead1703b573ed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER-REMOTE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cdai</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d77a89c68dff947</t>
+          <t>https://www.indeed.com/viewjob?jk=4692482ce562c2f3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luminie Studio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fa7f32e5b49cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=1badc32639c60a3b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Luminie Studio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67874b8838f9d9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=11fa7f32e5b49cfa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior ML Engineer / MLOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
+          <t>https://www.indeed.com/viewjob?jk=8577c851254cde7a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, IAM, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
+          <t>https://www.indeed.com/viewjob?jk=67874b8838f9d9a8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf37a9b3156f8dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcf77e4be9df296</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Developer-Full Stack Professional</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcb0ad10b28a6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd682ad6ededbf7</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -911,12 +911,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38db06205a3e4bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=caf37a9b3156f8dd</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b6929e731217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcb0ad10b28a6f6</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f1182f80665686</t>
+          <t>https://www.indeed.com/viewjob?jk=38db06205a3e4bf5</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1adbdb2bdac0514f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b6929e731217b8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Developer-Full Stack Professional</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd682ad6ededbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f1182f80665686</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Developer-Full Stack Senior</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Dask, Snowflake, PostgreSQL, NoSQL, ETL, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2f3d539abd0b18</t>
+          <t>https://www.indeed.com/viewjob?jk=1adbdb2bdac0514f</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Luminie Studio</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RELTIO INTEGRATION HUB ENGINEER</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
+          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ernest Talent</t>
+          <t>Luminie Studio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, Hive, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9362720734adf0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
+          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer .Net Full-Stack</t>
+          <t>RELTIO INTEGRATION HUB ENGINEER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8584f1ea91ecab5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e45fa699f911621</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer (Glue / Redshift / Python)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Ernest Talent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfe418b1f9d88e0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Engineer .Net Full-Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
+          <t>https://www.indeed.com/viewjob?jk=d8584f1ea91ecab5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qeexo, Co.</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Clemente, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d4975b9a0985a5be</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
+          <t>https://www.indeed.com/viewjob?jk=b13d0a86ba86e6de</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Qeexo, Co.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Clemente, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Academy Bank</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,77 +1606,77 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
+          <t>https://www.indeed.com/viewjob?jk=141e5928a75e80ea</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
+          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Cloud Platform)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Teambuilder</t>
+          <t>Academy Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d34ade42ca5e88</t>
+          <t>https://www.indeed.com/viewjob?jk=7624f31e61cc7e2c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Artificial Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
         </is>
       </c>
     </row>
@@ -1733,47 +1733,47 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Medisolv Inc</t>
+          <t>Nitka Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
+          <t>https://www.indeed.com/viewjob?jk=37d92c5876961093</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e500cf88e638ac7b</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
+          <t>GoLang Software Engineer, Identity Service- Freewheel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef1bee76953de15</t>
+          <t>https://www.indeed.com/viewjob?jk=911264091d15f95e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e996475c9120b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe29e41c637a7aef</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
+          <t>Senior DevOps Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Teambuilder</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c95bf56aa2f1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d34ade42ca5e88</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
+          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 3 (Contractor) 529701735</t>
+          <t>Cloud Solutions Architect 3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT, Tableau</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b55eb58f3e1bbe2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3ba3c7c3645334</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
+          <t>https://www.indeed.com/viewjob?jk=e500cf88e638ac7b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Georgetown, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef1bee76953de15</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (On Site-Only)</t>
+          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New York Cancer and Blood Specialists</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ridge, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e996475c9120b1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Solutions Architect 3 - CSA 26-06952</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, HDFS, Hive, Spark, Scala, PostgreSQL, Data Modeling, MLOps</t>
+          <t>IAM, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=50c95bf56aa2f1bd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Breakthrough)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
+          <t>https://www.indeed.com/viewjob?jk=4b89eb69d33d55d4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETL Engineer_Woonsocket, RI</t>
+          <t>Cloud Solutions Architect 3 (Contractor) 529701735</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
+          <t>IAM, Azure, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
+          <t>https://www.indeed.com/viewjob?jk=1b55eb58f3e1bbe2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
+          <t>https://www.indeed.com/viewjob?jk=362f92d7582e4290</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Full Stack Senior Developer/Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3684f4d626ff94f</t>
+          <t>https://www.indeed.com/viewjob?jk=a831ef17147e5fb9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Full Stack Senior Developer/Architect</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Belews Creek, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e87ee2317bc76f</t>
+          <t>https://www.indeed.com/viewjob?jk=a855e6b61c98aee1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GTM DevOps Engineer</t>
+          <t>Senior DevOps Engineer (On Site-Only)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>New York Cancer and Blood Specialists</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ridge, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, GCP, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63688985684ac528</t>
+          <t>https://www.indeed.com/viewjob?jk=89a332b33f5699d4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Holistic Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, S3, HDFS, Hive, Spark, Scala, PostgreSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
+          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer – Data Integration (Remote)</t>
+          <t>Senior Analytics Engineer (Breakthrough)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Engineer_Woonsocket, RI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Spark, PySpark, Scala, Kafka, Snowflake, ETL, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,137 +2421,137 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
+          <t>https://www.indeed.com/viewjob?jk=7979aeb406b6c268</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mongo Data Engineer</t>
+          <t>Data Architecture – Advisor II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, MongoDB, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3f517e79c6c989</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PineCone</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
+          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Java Full Stack Senior Developer/Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e3684f4d626ff94f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ping Engineer</t>
+          <t>Java Full Stack Senior Developer/Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e87ee2317bc76f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Application Engineer – AI &amp; Data</t>
+          <t>Data Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PaceMate™</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ML Administrator</t>
+          <t>Analytics Engineer, AV Safety Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Holistic Partners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7377fccc8d51edec</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solutions Architect, Customer Success - US (Remote)</t>
+          <t>Data Engineer – Data Integration (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,112 +2691,112 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
+          <t>https://www.indeed.com/viewjob?jk=b640e4ee2cfb05a2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
+          <t>https://www.indeed.com/viewjob?jk=048294938645b656</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Manger, Data Engineering</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb54c0674ca604fd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Senior Full-Stack Software Engineer, Clinical Intelligence</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>MEDecision</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,129 +2806,129 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd899653b72bc10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Application Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>PaceMate™</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1b381a515ef90e8e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer - Core Platform Integration</t>
+          <t>Ping Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Oracle, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb29602a924466f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, BigQuery, Dataflow, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
+          <t>https://www.indeed.com/viewjob?jk=adeb9523164787ec</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Senior Manger, Data Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7740c86dd5cb35b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Solution Architect</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kuvare Holdings LLC</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
+          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>cybertechnologyinnovations</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, SQL Server, MySQL, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e1a7ccf1662daf</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Application Developer – Microsoft .NET (Remote)</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
+          <t>https://www.indeed.com/viewjob?jk=a659bfcc72ba800b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
+          <t>https://www.indeed.com/viewjob?jk=000fc01861314bf7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack- FDE EST</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a24df4c2a49d56a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5be0d66e619d6c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Data Platform Solution Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Kuvare Holdings LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Scala, Kafka, Snowflake, MongoDB, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97dd0d3c2b0f1fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c51cbcb2f04411</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Application Developer – Microsoft .NET (Remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,129 +3331,129 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
+          <t>https://www.indeed.com/viewjob?jk=24964e45ccf8da68</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Sr. QA Automation Engineer- Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
+          <t>https://www.indeed.com/viewjob?jk=7952f8ac317de390</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Systems Analyst III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
+          <t>IAM, RDS, Azure, Snowflake, dbt, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
+          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
+          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Booker DiMaio, LLC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
+          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
+          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer (AWS) - Remote Opportunity</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Booker DiMaio, LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
+          <t>https://www.indeed.com/viewjob?jk=d8e2e1dcd00563f9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mazzella Companies</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
+          <t>https://www.indeed.com/viewjob?jk=a01faf411728a34c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Customer Data Platform Data Engineer (Hybrid)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4ef77ec35d25a4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ARUP Laboratories</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
+          <t>AWS, Scala, ELT, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
+          <t>https://www.indeed.com/viewjob?jk=8910d769e637e7b8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, Talend</t>
+          <t>AWS, Scala, ELT, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc5438c12ec9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=80e6175a2dcd61b4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Appian Systems Administrator</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b35afbe7938db70</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Redshift, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, Talend</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc5438c12ec9d4a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Priwils</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8004a61ef0799f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Senior Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
+          <t>https://www.indeed.com/viewjob?jk=78ebe266e21e63ac</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Automation Test Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Scala, ELT, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
+          <t>https://www.indeed.com/viewjob?jk=b31841b8cf3b4d68</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,17 +3951,262 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>AWS, Scala, ELT, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded756039a0a140f</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Recursion Technologies, Inc</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, HDFS, YARN, Spark, Scala, Kafka, ETL, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f69f1e8adbaaa70b</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior OAS/ODI Developer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>International Logic Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Fairfax, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f802008269dcfdc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior QA Automation Engineer – Enterprise Data &amp; Analytics Platform</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Priwils</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Adelphi, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b5210b167a792ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Automation Test Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Qualitest</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Snowflake, Oracle, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6aab560446e2d8ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed5c02fbbb94f50e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Engineer, Engineering Applications</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
         </is>
       </c>
     </row>
